--- a/templates/CAPIT ALFA FIRF - template.xlsx
+++ b/templates/CAPIT ALFA FIRF - template.xlsx
@@ -1,18 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="20355" yWindow="-11640" windowWidth="20730" windowHeight="11040" tabRatio="711" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Email" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Email" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="DataAnálise">Email!$A$1</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Email'!$B$7:$G$42</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Email'!$B$7:$G$43</definedName>
   </definedNames>
-  <calcPr calcId="191029" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -1254,7 +1254,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H45"/>
+  <dimension ref="A1:H46"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9.140625" defaultRowHeight="12.75"/>
   <cols>
     <col width="13.42578125" customWidth="1" style="2" min="1" max="1"/>
@@ -1262,8 +1262,8 @@
     <col width="5.42578125" customWidth="1" style="2" min="8" max="8"/>
     <col width="23.140625" bestFit="1" customWidth="1" style="2" min="9" max="9"/>
     <col width="23.42578125" bestFit="1" customWidth="1" style="2" min="10" max="10"/>
-    <col width="9.140625" customWidth="1" style="2" min="11" max="16"/>
-    <col width="9.140625" customWidth="1" style="2" min="17" max="16384"/>
+    <col width="9.140625" customWidth="1" style="2" min="11" max="17"/>
+    <col width="9.140625" customWidth="1" style="2" min="18" max="16384"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1420,23 +1420,23 @@
       <c r="A17" s="4" t="n"/>
       <c r="B17" s="10" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="C17" s="11" t="n">
-        <v>3.554201</v>
+        <v>3.5795842</v>
       </c>
       <c r="D17" s="12" t="n">
-        <v>0.0008296222507040429</v>
+        <v>0.0005043630830596779</v>
       </c>
       <c r="E17" s="12" t="n">
-        <v>0.0004643436842513005</v>
+        <v>0.0004027109948647745</v>
       </c>
       <c r="F17" s="12" t="n">
         <v>0.0005426623598601132</v>
       </c>
       <c r="G17" s="42" t="n">
-        <v>1.528800064404507</v>
+        <v>0.9294233769773381</v>
       </c>
       <c r="H17" s="4" t="n"/>
     </row>
@@ -1444,23 +1444,23 @@
       <c r="A18" s="4" t="n"/>
       <c r="B18" s="28" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="C18" s="29" t="n">
-        <v>3.5512548</v>
+        <v>3.5777797</v>
       </c>
       <c r="D18" s="30" t="n">
-        <v>-0.0002980592704427965</v>
+        <v>-2.895566772675995e-05</v>
       </c>
       <c r="E18" s="30" t="n">
-        <v>0.0004643436842513005</v>
+        <v>0.0004027109948647745</v>
       </c>
       <c r="F18" s="30" t="n">
         <v>0.0005426623598601132</v>
       </c>
       <c r="G18" s="31" t="n">
-        <v>-0.5492536289408939</v>
+        <v>-0.05335853353496657</v>
       </c>
       <c r="H18" s="4" t="n"/>
     </row>
@@ -1468,23 +1468,23 @@
       <c r="A19" s="4" t="n"/>
       <c r="B19" s="28" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="C19" s="29" t="n">
-        <v>3.5523136</v>
+        <v>3.5778833</v>
       </c>
       <c r="D19" s="30" t="n">
-        <v>0.0005111112694613507</v>
+        <v>0.0008873723840963077</v>
       </c>
       <c r="E19" s="30" t="n">
-        <v>0.0004643436842513005</v>
+        <v>0.0004027109948647745</v>
       </c>
       <c r="F19" s="30" t="n">
         <v>0.0005426623598601132</v>
       </c>
       <c r="G19" s="31" t="n">
-        <v>0.9418587085957173</v>
+        <v>1.635220073721445</v>
       </c>
       <c r="H19" s="4" t="n"/>
     </row>
@@ -1492,23 +1492,23 @@
       <c r="A20" s="4" t="n"/>
       <c r="B20" s="28" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="C20" s="29" t="n">
-        <v>3.5504989</v>
+        <v>3.5747112</v>
       </c>
       <c r="D20" s="30" t="n">
-        <v>0.0002216799560077476</v>
+        <v>-0.0002632806106500629</v>
       </c>
       <c r="E20" s="30" t="n">
-        <v>0.0004643436842513005</v>
+        <v>0.0004027109948647745</v>
       </c>
       <c r="F20" s="30" t="n">
         <v>0.0005426623598601132</v>
       </c>
       <c r="G20" s="31" t="n">
-        <v>0.4085043894787395</v>
+        <v>-0.4851646808854239</v>
       </c>
       <c r="H20" s="4" t="n"/>
     </row>
@@ -1516,23 +1516,23 @@
       <c r="A21" s="4" t="n"/>
       <c r="B21" s="28" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="C21" s="29" t="n">
-        <v>3.549712</v>
+        <v>3.5756526</v>
       </c>
       <c r="D21" s="30" t="n">
-        <v>-0.0003405313528218601</v>
+        <v>0.002147314833473635</v>
       </c>
       <c r="E21" s="30" t="n">
-        <v>0.0004643436842513005</v>
+        <v>0.0004027109948647745</v>
       </c>
       <c r="F21" s="30" t="n">
-        <v>0.0005513106415402369</v>
+        <v>0.0005426623598601132</v>
       </c>
       <c r="G21" s="31" t="n">
-        <v>-0.6176760018099645</v>
+        <v>3.956999770588781</v>
       </c>
       <c r="H21" s="4" t="n"/>
     </row>
@@ -1580,21 +1580,21 @@
       <c r="A24" s="4" t="n"/>
       <c r="B24" s="47" t="inlineStr">
         <is>
-          <t>Mar-26</t>
+          <t>Apr-26</t>
         </is>
       </c>
       <c r="C24" s="49" t="inlineStr"/>
       <c r="D24" s="12" t="n">
-        <v>0.01093902732686147</v>
+        <v>0.005774914414206744</v>
       </c>
       <c r="E24" s="16" t="n">
-        <v>0.008391257260208063</v>
+        <v>0.002822384949881185</v>
       </c>
       <c r="F24" s="16" t="n">
-        <v>0.00993531358511679</v>
+        <v>0.003804826246388782</v>
       </c>
       <c r="G24" s="17" t="n">
-        <v>1.101024867825839</v>
+        <v>1.517786632093332</v>
       </c>
       <c r="H24" s="18" t="n"/>
     </row>
@@ -1607,16 +1607,16 @@
       </c>
       <c r="C25" s="45" t="inlineStr"/>
       <c r="D25" s="30" t="n">
-        <v>0.01495175839300367</v>
+        <v>0.01079853069297521</v>
       </c>
       <c r="E25" s="32" t="n">
-        <v>0.01001161595968347</v>
+        <v>0.0115683699053577</v>
       </c>
       <c r="F25" s="32" t="n">
-        <v>0.01160659890087934</v>
+        <v>0.0115104208368324</v>
       </c>
       <c r="G25" s="33" t="n">
-        <v>1.28821186298347</v>
+        <v>0.9381525528954417</v>
       </c>
       <c r="H25" s="18" t="n"/>
     </row>
@@ -1629,16 +1629,16 @@
       </c>
       <c r="C26" s="45" t="inlineStr"/>
       <c r="D26" s="30" t="n">
-        <v>0.03856887575169998</v>
+        <v>0.04218698121155318</v>
       </c>
       <c r="E26" s="32" t="n">
-        <v>0.02809524341150937</v>
+        <v>0.03236919677502215</v>
       </c>
       <c r="F26" s="32" t="n">
-        <v>0.03529708637135154</v>
+        <v>0.03519865594435645</v>
       </c>
       <c r="G26" s="33" t="n">
-        <v>1.092692902352528</v>
+        <v>1.198539548732888</v>
       </c>
       <c r="H26" s="18" t="n"/>
     </row>
@@ -1651,16 +1651,16 @@
       </c>
       <c r="C27" s="45" t="inlineStr"/>
       <c r="D27" s="30" t="n">
-        <v>0.07516330804019056</v>
+        <v>0.07620562184325852</v>
       </c>
       <c r="E27" s="32" t="n">
-        <v>0.04787266347612573</v>
+        <v>0.05257486973565118</v>
       </c>
       <c r="F27" s="32" t="n">
-        <v>0.07187711571831934</v>
+        <v>0.07177520746070365</v>
       </c>
       <c r="G27" s="33" t="n">
-        <v>1.045719590846544</v>
+        <v>1.061726249763618</v>
       </c>
       <c r="H27" s="18" t="n"/>
     </row>
@@ -1673,16 +1673,16 @@
       </c>
       <c r="C28" s="45" t="inlineStr"/>
       <c r="D28" s="30" t="n">
-        <v>0.1495366180449447</v>
+        <v>0.1509608761926089</v>
       </c>
       <c r="E28" s="32" t="n">
-        <v>0.09198255784829135</v>
+        <v>0.09567969914036212</v>
       </c>
       <c r="F28" s="32" t="n">
-        <v>0.1477970366518437</v>
+        <v>0.148016036262707</v>
       </c>
       <c r="G28" s="33" t="n">
-        <v>1.011770069498746</v>
+        <v>1.01989541136391</v>
       </c>
       <c r="H28" s="18" t="n"/>
     </row>
@@ -1690,65 +1690,65 @@
       <c r="A29" s="28" t="n"/>
       <c r="B29" s="50" t="inlineStr">
         <is>
-          <t>Ano 2026</t>
+          <t>Últimos 720 dias</t>
         </is>
       </c>
       <c r="C29" s="45" t="inlineStr"/>
       <c r="D29" s="30" t="n">
-        <v>0.03532990200402208</v>
+        <v>0.2003553732889973</v>
       </c>
       <c r="E29" s="32" t="n">
-        <v>0.02587738721389243</v>
+        <v>0.2157632246490919</v>
       </c>
       <c r="F29" s="32" t="n">
-        <v>0.03187906296972676</v>
+        <v>0.2779304689804314</v>
       </c>
       <c r="G29" s="33" t="n">
-        <v>1.108247818876368</v>
+        <v>0.7208830828227905</v>
       </c>
       <c r="H29" s="18" t="n"/>
     </row>
-    <row r="30" ht="15.95" customHeight="1">
+    <row r="30" ht="15.95" customFormat="1" customHeight="1" s="27">
       <c r="A30" s="28" t="n"/>
       <c r="B30" s="50" t="inlineStr">
         <is>
-          <t>Ano 2025</t>
+          <t>Ano 2026</t>
         </is>
       </c>
       <c r="C30" s="45" t="inlineStr"/>
       <c r="D30" s="30" t="n">
-        <v>0.1479192695832172</v>
+        <v>0.04272396496459985</v>
       </c>
       <c r="E30" s="32" t="n">
-        <v>0.09645253008809984</v>
+        <v>0.03422875935893455</v>
       </c>
       <c r="F30" s="32" t="n">
-        <v>0.143132751155109</v>
+        <v>0.0380553842733744</v>
       </c>
       <c r="G30" s="33" t="n">
-        <v>1.033441112460147</v>
-      </c>
-      <c r="H30" s="58" t="n"/>
+        <v>1.122678584919502</v>
+      </c>
+      <c r="H30" s="18" t="n"/>
     </row>
     <row r="31" ht="15.95" customHeight="1">
       <c r="A31" s="28" t="n"/>
       <c r="B31" s="50" t="inlineStr">
         <is>
-          <t>Ano 2024</t>
+          <t>Ano 2025</t>
         </is>
       </c>
       <c r="C31" s="45" t="inlineStr"/>
       <c r="D31" s="30" t="n">
-        <v>0.03937422528438894</v>
+        <v>0.1479192695832172</v>
       </c>
       <c r="E31" s="32" t="n">
-        <v>0.1034950040687741</v>
+        <v>0.09645253008809984</v>
       </c>
       <c r="F31" s="32" t="n">
-        <v>0.1092049264357533</v>
+        <v>0.143132751155109</v>
       </c>
       <c r="G31" s="33" t="n">
-        <v>0.3605535626412726</v>
+        <v>1.033441112460147</v>
       </c>
       <c r="H31" s="58" t="n"/>
     </row>
@@ -1756,187 +1756,209 @@
       <c r="A32" s="28" t="n"/>
       <c r="B32" s="50" t="inlineStr">
         <is>
-          <t>Acumulado²</t>
+          <t>Ano 2024</t>
         </is>
       </c>
       <c r="C32" s="45" t="inlineStr"/>
       <c r="D32" s="30" t="n">
-        <v>2.554201</v>
+        <v>0.03937422528438894</v>
       </c>
       <c r="E32" s="32" t="n">
-        <v>3.162484441247527</v>
+        <v>0.1034950040687741</v>
       </c>
       <c r="F32" s="32" t="n">
-        <v>2.460876811712316</v>
+        <v>0.1092049264357533</v>
       </c>
       <c r="G32" s="33" t="n">
-        <v>1.037923145052819</v>
+        <v>0.3605535626412726</v>
       </c>
       <c r="H32" s="58" t="n"/>
     </row>
     <row r="33" ht="15.95" customHeight="1">
-      <c r="A33" s="4" t="n"/>
-      <c r="B33" s="20" t="n"/>
-      <c r="C33" s="14" t="n"/>
-      <c r="D33" s="14" t="n"/>
-      <c r="E33" s="14" t="n"/>
-      <c r="F33" s="14" t="n"/>
-      <c r="G33" s="14" t="n"/>
-      <c r="H33" s="4" t="n"/>
-    </row>
-    <row r="34" ht="26.1" customHeight="1">
-      <c r="B34" s="53" t="inlineStr">
+      <c r="A33" s="28" t="n"/>
+      <c r="B33" s="50" t="inlineStr">
+        <is>
+          <t>Acumulado²</t>
+        </is>
+      </c>
+      <c r="C33" s="45" t="inlineStr"/>
+      <c r="D33" s="30" t="n">
+        <v>2.5795842</v>
+      </c>
+      <c r="E33" s="32" t="n">
+        <v>3.196370027429726</v>
+      </c>
+      <c r="F33" s="32" t="n">
+        <v>2.481591920632116</v>
+      </c>
+      <c r="G33" s="33" t="n">
+        <v>1.039487668602227</v>
+      </c>
+      <c r="H33" s="58" t="n"/>
+    </row>
+    <row r="34" ht="15.95" customHeight="1">
+      <c r="A34" s="4" t="n"/>
+      <c r="B34" s="20" t="n"/>
+      <c r="C34" s="14" t="n"/>
+      <c r="D34" s="14" t="n"/>
+      <c r="E34" s="14" t="n"/>
+      <c r="F34" s="14" t="n"/>
+      <c r="G34" s="14" t="n"/>
+      <c r="H34" s="4" t="n"/>
+    </row>
+    <row r="35" ht="26.1" customHeight="1">
+      <c r="B35" s="53" t="inlineStr">
         <is>
           <t>Patrimônio Líquido (R$)</t>
         </is>
       </c>
-      <c r="C34" s="53" t="n"/>
-      <c r="D34" s="53" t="n"/>
-      <c r="E34" s="53" t="n"/>
-      <c r="F34" s="53" t="n"/>
-      <c r="G34" s="53" t="n"/>
-      <c r="H34" s="4" t="n"/>
-    </row>
-    <row r="35" ht="15.95" customHeight="1">
-      <c r="B35" s="34" t="inlineStr">
+      <c r="C35" s="53" t="n"/>
+      <c r="D35" s="53" t="n"/>
+      <c r="E35" s="53" t="n"/>
+      <c r="F35" s="53" t="n"/>
+      <c r="G35" s="53" t="n"/>
+      <c r="H35" s="4" t="n"/>
+    </row>
+    <row r="36" ht="15.95" customHeight="1">
+      <c r="B36" s="34" t="inlineStr">
         <is>
           <t>Hoje¹</t>
-        </is>
-      </c>
-      <c r="C35" s="35" t="n"/>
-      <c r="D35" s="35" t="n"/>
-      <c r="E35" s="46" t="n">
-        <v>67547800.81</v>
-      </c>
-      <c r="F35" s="46" t="n"/>
-      <c r="G35" s="46" t="n"/>
-      <c r="H35" s="4" t="n"/>
-    </row>
-    <row r="36" ht="15.95" customHeight="1">
-      <c r="B36" s="36" t="inlineStr">
-        <is>
-          <t>Últimos 12 Meses (Média Diária)¹</t>
         </is>
       </c>
       <c r="C36" s="35" t="n"/>
       <c r="D36" s="35" t="n"/>
       <c r="E36" s="46" t="n">
-        <v>73995062.46349207</v>
+        <v>68030209.29000001</v>
       </c>
       <c r="F36" s="46" t="n"/>
       <c r="G36" s="46" t="n"/>
       <c r="H36" s="4" t="n"/>
     </row>
     <row r="37" ht="15.95" customHeight="1">
-      <c r="B37" s="34" t="n"/>
+      <c r="B37" s="36" t="inlineStr">
+        <is>
+          <t>Últimos 12 Meses (Média Diária)¹</t>
+        </is>
+      </c>
       <c r="C37" s="35" t="n"/>
       <c r="D37" s="35" t="n"/>
-      <c r="E37" s="35" t="n"/>
-      <c r="F37" s="35" t="n"/>
-      <c r="G37" s="35" t="n"/>
+      <c r="E37" s="46" t="n">
+        <v>73877116.0136508</v>
+      </c>
+      <c r="F37" s="46" t="n"/>
+      <c r="G37" s="46" t="n"/>
       <c r="H37" s="4" t="n"/>
     </row>
     <row r="38" ht="15.95" customHeight="1">
-      <c r="A38" s="4" t="n"/>
-      <c r="B38" s="37" t="inlineStr">
-        <is>
-          <t>¹Data de Referência:</t>
-        </is>
-      </c>
-      <c r="C38" s="43" t="inlineStr">
-        <is>
-          <t>2026-03-25</t>
-        </is>
-      </c>
-      <c r="D38" s="38" t="n"/>
-      <c r="E38" s="38" t="n"/>
-      <c r="F38" s="38" t="n"/>
-      <c r="G38" s="38" t="n"/>
+      <c r="B38" s="34" t="n"/>
+      <c r="C38" s="35" t="n"/>
+      <c r="D38" s="35" t="n"/>
+      <c r="E38" s="35" t="n"/>
+      <c r="F38" s="35" t="n"/>
+      <c r="G38" s="35" t="n"/>
       <c r="H38" s="4" t="n"/>
     </row>
     <row r="39" ht="15.95" customHeight="1">
       <c r="A39" s="4" t="n"/>
-      <c r="B39" s="39" t="inlineStr">
-        <is>
-          <t xml:space="preserve">² Cota Inicial em: </t>
+      <c r="B39" s="37" t="inlineStr">
+        <is>
+          <t>¹Data de Referência:</t>
         </is>
       </c>
       <c r="C39" s="43" t="inlineStr">
         <is>
-          <t>2012-10-22</t>
-        </is>
-      </c>
-      <c r="D39" s="40" t="n"/>
-      <c r="E39" s="40" t="n"/>
-      <c r="F39" s="40" t="n"/>
-      <c r="G39" s="40" t="n"/>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="D39" s="38" t="n"/>
+      <c r="E39" s="38" t="n"/>
+      <c r="F39" s="38" t="n"/>
+      <c r="G39" s="38" t="n"/>
       <c r="H39" s="4" t="n"/>
     </row>
     <row r="40" ht="15.95" customHeight="1">
       <c r="A40" s="4" t="n"/>
-      <c r="B40" s="22" t="n"/>
-      <c r="C40" s="21" t="n"/>
-      <c r="D40" s="23" t="n"/>
-      <c r="E40" s="23" t="n"/>
-      <c r="F40" s="23" t="n"/>
-      <c r="G40" s="23" t="n"/>
+      <c r="B40" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">² Cota Inicial em: </t>
+        </is>
+      </c>
+      <c r="C40" s="43" t="inlineStr">
+        <is>
+          <t>2012-10-22</t>
+        </is>
+      </c>
+      <c r="D40" s="40" t="n"/>
+      <c r="E40" s="40" t="n"/>
+      <c r="F40" s="40" t="n"/>
+      <c r="G40" s="40" t="n"/>
       <c r="H40" s="4" t="n"/>
     </row>
-    <row r="41" ht="40.5" customHeight="1">
+    <row r="41" ht="15.95" customHeight="1">
       <c r="A41" s="4" t="n"/>
-      <c r="B41" s="52" t="inlineStr">
+      <c r="B41" s="22" t="n"/>
+      <c r="C41" s="21" t="n"/>
+      <c r="D41" s="23" t="n"/>
+      <c r="E41" s="23" t="n"/>
+      <c r="F41" s="23" t="n"/>
+      <c r="G41" s="23" t="n"/>
+      <c r="H41" s="4" t="n"/>
+    </row>
+    <row r="42" ht="40.5" customHeight="1">
+      <c r="A42" s="4" t="n"/>
+      <c r="B42" s="52" t="inlineStr">
         <is>
           <t>As informações contidas neste material são de caráter exclusivamente informativo. Fundos de investimento não contam com garantia do administrador do fundo, do gestor da carteira, de qualquer mecanismo de seguro ou, ainda, do Fundo Garantidor de Créditos – FGC. Rentabilidade passada não representa garantia de rentabilidade futura. "A rentabilidade divulgada não é líquida de impostos.“ Leia o prospecto e o regulamento antes de investir.</t>
         </is>
       </c>
-      <c r="C41" s="52" t="n"/>
-      <c r="D41" s="52" t="n"/>
-      <c r="E41" s="52" t="n"/>
-      <c r="F41" s="52" t="n"/>
-      <c r="G41" s="52" t="n"/>
-      <c r="H41" s="4" t="n"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="4" t="n"/>
-      <c r="B42" s="51" t="n"/>
-      <c r="C42" s="51" t="n"/>
-      <c r="D42" s="51" t="n"/>
-      <c r="E42" s="51" t="n"/>
-      <c r="F42" s="51" t="n"/>
-      <c r="G42" s="51" t="n"/>
+      <c r="C42" s="52" t="n"/>
+      <c r="D42" s="52" t="n"/>
+      <c r="E42" s="52" t="n"/>
+      <c r="F42" s="52" t="n"/>
+      <c r="G42" s="52" t="n"/>
       <c r="H42" s="4" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="4" t="n"/>
-      <c r="B43" s="24" t="n"/>
-      <c r="C43" s="24" t="n"/>
-      <c r="D43" s="24" t="n"/>
-      <c r="E43" s="24" t="n"/>
-      <c r="F43" s="24" t="n"/>
-      <c r="G43" s="24" t="n"/>
+      <c r="B43" s="51" t="n"/>
+      <c r="C43" s="51" t="n"/>
+      <c r="D43" s="51" t="n"/>
+      <c r="E43" s="51" t="n"/>
+      <c r="F43" s="51" t="n"/>
+      <c r="G43" s="51" t="n"/>
       <c r="H43" s="4" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="4" t="n"/>
-      <c r="B44" s="25" t="n"/>
-      <c r="C44" s="26" t="n"/>
-      <c r="D44" s="19" t="n"/>
-      <c r="E44" s="19" t="n"/>
-      <c r="F44" s="19" t="n"/>
-      <c r="G44" s="19" t="n"/>
+      <c r="B44" s="24" t="n"/>
+      <c r="C44" s="24" t="n"/>
+      <c r="D44" s="24" t="n"/>
+      <c r="E44" s="24" t="n"/>
+      <c r="F44" s="24" t="n"/>
+      <c r="G44" s="24" t="n"/>
       <c r="H44" s="4" t="n"/>
     </row>
     <row r="45">
+      <c r="A45" s="4" t="n"/>
       <c r="B45" s="25" t="n"/>
       <c r="C45" s="26" t="n"/>
       <c r="D45" s="19" t="n"/>
       <c r="E45" s="19" t="n"/>
       <c r="F45" s="19" t="n"/>
       <c r="G45" s="19" t="n"/>
+      <c r="H45" s="4" t="n"/>
+    </row>
+    <row r="46">
+      <c r="B46" s="25" t="n"/>
+      <c r="C46" s="26" t="n"/>
+      <c r="D46" s="19" t="n"/>
+      <c r="E46" s="19" t="n"/>
+      <c r="F46" s="19" t="n"/>
+      <c r="G46" s="19" t="n"/>
     </row>
   </sheetData>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" paperSize="9" scale="88" fitToHeight="1" fitToWidth="1"/>
+  <pageSetup orientation="landscape" paperSize="9" scale="86"/>
 </worksheet>
 </file>